--- a/meta/program/BlancoValueObjectFieldStructure.xlsx
+++ b/meta/program/BlancoValueObjectFieldStructure.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tueda/data/webstorm/blanco/blancoValueObject/meta/program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AB6DD5-470B-2F45-8A0F-189552833864}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147237C9-329B-534A-8E6C-75C99A04DD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1860" windowWidth="28300" windowHeight="17440" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>バリューオブジェクト定義書</t>
   </si>
@@ -397,6 +397,17 @@
   </si>
   <si>
     <t>fixedValue</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>constArg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コンストラクタ引数かどうか</t>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">ヒキスウ </t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1351,7 +1362,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1666,7 +1677,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="40">
-        <f t="shared" ref="A29:A44" si="0">A28+1</f>
+        <f t="shared" ref="A29:A43" si="0">A28+1</f>
         <v>3</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -1946,8 +1957,8 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="40">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>A42+1</f>
+        <v>17</v>
       </c>
       <c r="B44" s="41" t="s">
         <v>54</v>
@@ -1963,15 +1974,32 @@
       <c r="G44"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="22"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="25"/>
+      <c r="A45" s="40">
+        <f>A43+1</f>
+        <v>18</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="43"/>
       <c r="G45"/>
     </row>
     <row r="46" spans="1:7">
+      <c r="A46" s="22"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="25"/>
       <c r="G46"/>
     </row>
     <row r="47" spans="1:7">
@@ -1979,6 +2007,9 @@
     </row>
     <row r="48" spans="1:7">
       <c r="G48"/>
+    </row>
+    <row r="49" spans="7:7">
+      <c r="G49"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1996,7 +2027,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D61" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D62" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>型</formula1>
       <formula2>0</formula2>
     </dataValidation>
